--- a/important_mails_2026-10-31.xlsx
+++ b/important_mails_2026-10-31.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,125 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 30 Oct 2026 19:02:00 +0000</t>
+          <t>Sat, 31 Oct 2026 10:07:18 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (JzQCgQ3wPF)</t>
+          <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 31 Oct 2026 09:18:19 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amazon.de/gp/cart/view.html?ref_=cor
+145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
+ 49,95 €
+https://www.amazon.de/gp/product/B0H11DGDRL/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+Roaxkois Keramik Bemalen Set - Kreatives Keramik Bastelset mit Farben, Pinseln und Anleitungen, Perfektes Tassen Bemalen Set für individuelle Geschenke und Freizeitgestaltung
+ 19,95 €
+https://www.amazon.de/gp/product/B0FD8PWPNK/?ref_=ci_mcx_mr_2p_0_lm
+Pott&amp;#x27;d Tassen zum Bemalen, Keramik Bemalen Set für Erwachsene | Tassen Bemalen Set für Anfänger mit Tassen, Farben, Pinseln und Anleitung, Kreative DIY Geschenkidee
+ 39,00 €
+https://www.amazon.de/gp/product/B0FVY9ZQ3K/?ref_=ci_mcx_mr_2p_1_lm
+Keramik Bemalen Set Tasse Bemalen Set DIY Tassen Malset Kreatives Geschenk | für Erwachsene Enthält 2*Tassen, 2*Farbwanne, 4*Pinsel, 2 * 12 Farben und Anleitung
+ -20 % 23,99 € UVP: 29,99 €
+https://www.amazon.de/gp/product/B0GF995KHV/?ref_=ci_mcx_mr_2p_2_lm
+STRUCT® Keramik Bemalen Set - mit 2x Tassen </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 30 Oct 2026 19:02:00 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (JzQCgQ3wPF)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -534,39 +638,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 17:06:52 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience.
@@ -580,39 +684,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 06:24:04 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Adrian_Juarezxnl@mail.com</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Urgent: Unauthorized use of [APEX] intellectual property</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Hello,
  This message comes from the intellectual property protection team at [ZENITH]. It has come to our attention that your current storefront listing is using our copyrighted images and trademarked brand name without authorization.
@@ -626,39 +730,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 10:00:25 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (J/7a1uvCq9)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -678,39 +782,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 27 Oct 2026 09:11:14 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -726,39 +830,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Tue, 27 Oct 2026 06:05:57 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -774,39 +878,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Mon, 26 Oct 2026 21:52:50 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (jMekAFT184)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -826,39 +930,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mon, 26 Oct 2026 06:03:41 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -874,39 +978,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 14:51:23 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -922,39 +1026,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 17:02:55 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -971,39 +1075,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sat, 24 Oct 2026 13:43:57 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1026,39 +1130,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 19:06:51 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -1077,39 +1181,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 10:06:52 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1127,39 +1231,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 05:44:22 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"gpsr-rspaduit-cn-seller-compliance@amazon.com" &lt;gpsr-rspaduit-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13434500502] 【立刻采取行动】续签您的欧盟负责人合同以避免产品被下架</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13434500502] 【立刻采取行动】续签您的欧盟负责人合同以避免产品被下架
@@ -1178,39 +1282,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 05:44:16 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>gpsr-rspaduit-cn-seller-compliance@amazon.com</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Resolution for CaseID: 13434500502</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 Resolution for CaseID: 13434500502
@@ -1230,39 +1334,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 23:58:37 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon New Product Success &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>The New Product Success Monthly | October</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Use the power of Amazon first-party data for your new product launches
@@ -1280,39 +1384,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 21:27:23 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"epr-sp-appeals-3p@amazon.co.uk" &lt;epr-sp-appeals-3p@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13435312252] 想咨询为什么波兰包装法一直不通过</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 13435312252] 想咨询为什么波兰包装法一直不通过
@@ -1345,39 +1449,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 10:06:44 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1395,39 +1499,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 09:14:11 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"gpsr-rspaduit-cn-seller-compliance@amazon.com" &lt;gpsr-rspaduit-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13434500502] 【立刻采取行动】续签您的欧盟负责人合同以避免产品被下架</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13434500502] 【立刻采取行动】续签您的欧盟负责人合同以避免产品被下架
@@ -1454,39 +1558,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 07:05:55 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -1505,39 +1609,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 08:11:15 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -1561,40 +1665,40 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 27 Oct 2026 11:06:20 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit Saudi Arabia Product Safety Law details through Account
  Health</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  You can now submit the required Product Safety Law information via Account Health
@@ -1613,39 +1717,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 26 Oct 2026 18:10:20 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Seller News: October 2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Our Seller Newsletter provides the most important policy, tool, and program updates from the past month.
  96
@@ -1654,39 +1758,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 26 Oct 2026 10:31:49 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Seller News: October 2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Our Seller Newsletter provides the most important policy, tool and programme updates from the past month.
  96
@@ -1695,39 +1799,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 19:03:15 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para noviembre</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para noviembre
@@ -1760,39 +1864,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 18:53:42 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>New EU customs handling fee from Nov 1</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">New EU customs handling fee from Nov 1
  96
@@ -1801,39 +1905,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 16:16:02 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Temporary peak season extensions for international FBA shipments</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Review the updated the abandoned shipment and automatic shipment closure windows for international shipments.
@@ -1847,39 +1951,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 09:28:55 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1898,39 +2002,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 08:18:26 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>The Fulfilment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Reduce your inventory storage fees today</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1950,40 +2054,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 00:18:16 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Vendita su Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Esegui il tuo piano personalizzato per la Settimana del Black
  Friday entro il giorno 2026/11/18</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Buongiorno,
@@ -1998,40 +2102,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 20:33:11 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Vender en Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Lleva a cabo tu plan personalizado para la semana del Black Friday
  antes del 2026/11/18</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Hola:
@@ -2048,39 +2152,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 15:18:40 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Support Vendeur Amazon &lt;merch.service05@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13436065042&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13436065042&lt;/p&gt;
@@ -2095,39 +2199,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 29 Oct 2026 02:41:56 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知（请勿回复） &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>亚马逊已配送您售出的商品</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  我们已完成您亚马逊物流订单的处理和配送。
@@ -2167,40 +2271,40 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 13:43:48 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Soluciona los errores de precio para restablecer los listings
  desactivados.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Eliminar errores de precio
@@ -2222,39 +2326,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 13:10:11 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Le tue offerte sono state disattivate</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Le tue offerte sono state disattivate
@@ -2275,39 +2379,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 12:08:23 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Le tue offerte sono state disattivate</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Le tue offerte sono state disattivate
@@ -2334,39 +2438,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 12:04:51 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Vos mises en vente ont été désactivées</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Vos mises en vente ont été désactivées
@@ -2385,39 +2489,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 08:08:14 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Le tue offerte sono state disattivate</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Le tue offerte sono state disattivate
@@ -2444,39 +2548,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Wed, 28 Oct 2026 08:04:57 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Vos mises en vente ont été désactivées</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Vos mises en vente ont été désactivées
@@ -2495,39 +2599,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 27 Oct 2026 07:19:19 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -2549,39 +2653,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 10:24:51 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2605,39 +2709,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 10:12:09 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2660,39 +2764,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 30 Oct 2026 09:08:14 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-11-12</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2713,40 +2817,40 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 26 Oct 2026 08:30:50 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13389411022]"Your Case Resolved" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13389411022]"Your Case Resolved" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -2762,115 +2866,6 @@
 - Split your next shipment between FBA and upstream storage via Amazon Warehousing and Distribution (AWD). More info: https://sellercentral-europe.amazon.com/help/hub/reference/GF6ZC8VEBM7HCEGV
  Create shipment and send to AWD: https://sellercentral-europe.amazon.com/asdn/about
 - Run promotions on slow-movin</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 24 Oct 2026 04:18:18 +0000</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-11-05</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-11-05 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0GYPZ58JY Quantity: 2
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 24 Oct 2026 04:12:00 +0000</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- uncUgm1HCf
- Unsellable Products:
-- FNSKU: B0DRC8LPGS Quantity: 1
-- FNSKU: X0023C0TBV Quantity: 2
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferen</t>
         </is>
       </c>
     </row>
@@ -12557,22 +12552,131 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
+          <t>Sat, 24 Oct 2026 04:18:18 +0000</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-11-05</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-11-05 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0GYPZ58JY Quantity: 2
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 24 Oct 2026 04:12:00 +0000</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- uncUgm1HCf
+ Unsellable Products:
+- FNSKU: B0DRC8LPGS Quantity: 1
+- FNSKU: X0023C0TBV Quantity: 2
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
           <t>Tue, 20 Oct 2026 08:30:54 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13389411022]"Your Help Needed" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13389411022]"Your Help Needed" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -12590,39 +12694,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Sat, 17 Oct 2026 04:18:17 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-29</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12643,39 +12747,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Sat, 17 Oct 2026 04:16:43 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-29</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12698,39 +12802,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Sat, 17 Oct 2026 03:57:58 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12754,40 +12858,40 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 08:25:20 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13389411022] Optimize Your Next EU FBA Shipment Based on
  Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 13389411022] Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -12803,39 +12907,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 03:51:55 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-22</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12857,39 +12961,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 03:37:48 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12913,39 +13017,39 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 20:20:03 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -12961,39 +13065,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 20:33:01 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -13009,39 +13113,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 03:07:33 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-15</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13065,39 +13169,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 17:08:31 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -13111,39 +13215,39 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 14:07:48 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13172,39 +13276,39 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 02:02:21 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon Business &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Earn new Business Discount badge for always-on visibility</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>96
  New badge launches in two weeks - set your Business Price at least 5% below standard retail price to get started
@@ -13217,39 +13321,39 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 09:43:53 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13278,39 +13382,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 21:27:08 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>A passkey is required for account access starting in two weeks</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>96
  For security, set up passkey login to maintain account access
@@ -13326,39 +13430,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 04:58:43 +0000</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>A returns experience customers actually like</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>96
  Faster resolutions for buyers, less friction for you.
@@ -13383,39 +13487,39 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 00:17:41 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>View your US Q4-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q4-2026
